--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-05-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_05-05-2026.xlsx
@@ -1232,7 +1232,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£51.7</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£40.67</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£65.57</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
